--- a/data/trans_dic/IP31KM07_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM07_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>89,54%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83,39; 93,91</t>
+          <t>83,75; 93,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73,18; 92,39</t>
+          <t>82,57; 93,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80,33; 91,89</t>
+          <t>85,63; 93,06</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,34%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,98; 96,12</t>
+          <t>85,25; 95,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,47; 95,7</t>
+          <t>87,48; 96,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88,02; 95,04</t>
+          <t>88,49; 95,07</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>92,99%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>78,32; 95,98</t>
+          <t>87,7; 98,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78,11; 97,25</t>
+          <t>80,9; 96,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82,47; 95,38</t>
+          <t>87,82; 96,29</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>87,34%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51,98; 93,2</t>
+          <t>76,49; 90,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,9; 90,95</t>
+          <t>84,01; 93,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64,87; 90,07</t>
+          <t>82,38; 91,02</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>85,67%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>74,76; 90,33</t>
+          <t>76,94; 90,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77,83; 90,14</t>
+          <t>81,57; 91,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>79,33; 89,08</t>
+          <t>80,91; 89,73</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>92,17%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89,34; 98,24</t>
+          <t>78,48; 95,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>79,64; 94,78</t>
+          <t>88,73; 98,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86,84; 95,35</t>
+          <t>87,05; 95,69</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>89,09%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>72,66; 91,19</t>
+          <t>84,8; 90,51</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>83,32; 89,85</t>
+          <t>88,08; 92,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81,02; 89,51</t>
+          <t>87,15; 90,74</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>137</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>91116</t>
+          <t>108956</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>117102</t>
+          <t>89438</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>208219</t>
+          <t>198394</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>84814; 95515</t>
+          <t>101516; 113788</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>98927; 124884</t>
+          <t>82854; 93714</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>190294; 217670</t>
+          <t>189719; 206181</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>127</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>86524</t>
+          <t>82321</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>85817</t>
+          <t>88782</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>172341</t>
+          <t>171102</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81233; 89773</t>
+          <t>76622; 86042</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80093; 89681</t>
+          <t>83466; 91918</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>164695; 177818</t>
+          <t>163957; 176151</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>65</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>44834</t>
+          <t>53047</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>57331</t>
+          <t>47243</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102164</t>
+          <t>100289</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>39231; 48077</t>
+          <t>48975; 54941</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>48690; 60618</t>
+          <t>42075; 50153</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>92717; 107229</t>
+          <t>94718; 103849</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>247</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>173818</t>
+          <t>167929</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>181202</t>
+          <t>158675</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>355021</t>
+          <t>326604</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>112044; 200873</t>
+          <t>150920; 178130</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>163539; 193415</t>
+          <t>148388; 165093</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>277770; 385659</t>
+          <t>308047; 340371</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>149</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>97830</t>
+          <t>123060</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>134860</t>
+          <t>100572</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>232690</t>
+          <t>223632</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>86360; 104336</t>
+          <t>112008; 131081</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>124105; 143737</t>
+          <t>94185; 105561</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>218142; 244952</t>
+          <t>211218; 234243</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>94</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>65576</t>
+          <t>58534</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>60983</t>
+          <t>67018</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>126558</t>
+          <t>125553</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>61552; 67681</t>
+          <t>51688; 62582</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>54976; 65427</t>
+          <t>62429; 69388</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>119776; 131516</t>
+          <t>118576; 130355</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>819</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>826</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>559698</t>
+          <t>593846</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>637295</t>
+          <t>551729</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1196992</t>
+          <t>1145575</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>468747; 588320</t>
+          <t>572958; 611573</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>610235; 658050</t>
+          <t>537465; 563203</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1116118; 1233026</t>
+          <t>1120677; 1166814</t>
         </is>
       </c>
     </row>
